--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -591,7 +591,13 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
+  </si>
+  <si>
+    <t>1488: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.BacteriologyReportStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -607,12 +613,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1488: terminologyMaps using null on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.BacteriologyReportStatus</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -695,6 +695,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>1525: fixed value = http://loinc.org#42803-7 Bacteria identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -711,9 +714,6 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>1525: fixed value = http://loinc.org#42803-7 Bacteria identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1012,16 +1012,16 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>1516: terminologyMaps using null on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.UrineScreen</t>
+  </si>
+  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1516: terminologyMaps using null on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.UrineScreen</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.text</t>
@@ -1526,11 +1526,11 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
+    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5+to+160)</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5+to+160)</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -1931,7 +1931,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1941,14 +1941,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2187,22 +2187,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -2824,13 +2824,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -2950,13 +2950,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3076,13 +3076,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3204,13 +3204,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3321,25 +3321,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3447,22 +3447,22 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3573,22 +3573,22 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3714,13 +3714,13 @@
         <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AR14" t="s" s="2">
-        <v>191</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3834,16 +3834,16 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AO15" t="s" s="2">
+      <c r="AQ15" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3964,16 +3964,16 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AO16" t="s" s="2">
+      <c r="AQ16" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -4086,25 +4086,25 @@
         <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AP17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AQ17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4211,25 +4211,25 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4343,19 +4343,19 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4465,25 +4465,25 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4593,25 +4593,25 @@
         <v>258</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4725,19 +4725,19 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4845,25 +4845,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4974,25 +4974,25 @@
         <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -5104,25 +5104,25 @@
         <v>84</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR25" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5234,13 +5234,13 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5360,13 +5360,13 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5479,28 +5479,28 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>316</v>
+        <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>318</v>
+        <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>319</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5613,16 +5613,16 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5737,28 +5737,28 @@
         <v>288</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5869,16 +5869,16 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -5994,25 +5994,25 @@
         <v>84</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP32" t="s" s="2">
+      <c r="AQ32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR32" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -6125,16 +6125,16 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6248,25 +6248,25 @@
         <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6379,16 +6379,16 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6502,25 +6502,25 @@
         <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
+      <c r="AQ36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR36" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR36" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -6628,25 +6628,25 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6759,16 +6759,16 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6886,13 +6886,13 @@
         <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7012,13 +7012,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7140,13 +7140,13 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7261,16 +7261,16 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7385,16 +7385,16 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7510,19 +7510,19 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7638,19 +7638,19 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7770,13 +7770,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7891,16 +7891,16 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8017,16 +8017,16 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8143,16 +8143,16 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8271,16 +8271,16 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8398,13 +8398,13 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8524,13 +8524,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8652,13 +8652,13 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8771,25 +8771,25 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>84</v>
+        <v>480</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>480</v>
+        <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ54" t="s" s="2">
-        <v>481</v>
+        <v>221</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -8900,25 +8900,25 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
+      <c r="AQ55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR55" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -9027,28 +9027,28 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
+      <c r="AQ56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9161,16 +9161,16 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AP57" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9283,28 +9283,28 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
+      <c r="AQ58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR58" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AR58" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9417,16 +9417,16 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,10 +591,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
-  </si>
-  <si>
-    <t>1488: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+  </si>
+  <si>
+    <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
   </si>
   <si>
     <t>Micro.Microbiology.BacteriologyReportStatus</t>
@@ -1931,7 +1931,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.65234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="573">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,6 +515,209 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>Observation.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Observation.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>Observation.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>1476: source value from MICROBIOLOGY - IEN (#63.05-.001)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>Observation.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>Observation.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>Observation.basedOn</t>
   </si>
   <si>
@@ -588,9 +791,6 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
   </si>
   <si>
@@ -618,10 +818,6 @@
     <t>Observation.category</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Classification of  type of observation</t>
   </si>
   <si>
@@ -632,31 +828,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -667,6 +838,31 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -686,9 +882,6 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>LOINC codes</t>
   </si>
   <si>
@@ -714,6 +907,67 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -735,6 +989,12 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -824,6 +1084,10 @@
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">us-core-1
 </t>
   </si>
@@ -844,6 +1108,22 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
+  </si>
+  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -860,6 +1140,12 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
+    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.ReportCompletedDateTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -885,6 +1171,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -916,10 +1205,6 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t>obs-7
 us-core-2us-core-3us-core-4</t>
   </si>
@@ -952,103 +1237,28 @@
     <t>Observation.value[x].id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.value[x]:valueCodeableConcept.extension</t>
   </si>
   <si>
     <t>Observation.value[x].extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.value[x]:valueCodeableConcept.coding</t>
   </si>
   <si>
     <t>Observation.value[x].coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
     <t>1516: terminologyMaps using null on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
   </si>
   <si>
     <t>Micro.Microbiology.UrineScreen</t>
   </si>
   <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
     <t>Observation.value[x]:valueCodeableConcept.text</t>
   </si>
   <si>
     <t>Observation.value[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.value[x]:valueString</t>
@@ -1145,6 +1355,12 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
+    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.SpecimenComment</t>
+  </si>
+  <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
@@ -1226,6 +1442,12 @@
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+  </si>
+  <si>
+    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.MicrobiologyAccession</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -1903,7 +2125,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR59"/>
+  <dimension ref="A1:AR72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
@@ -1925,12 +2147,12 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1942,7 +2164,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -3354,14 +3576,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>84</v>
@@ -3370,21 +3592,19 @@
         <v>84</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>84</v>
       </c>
@@ -3432,19 +3652,19 @@
         <v>84</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>84</v>
@@ -3453,16 +3673,16 @@
         <v>84</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>167</v>
+        <v>84</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3473,14 +3693,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3496,19 +3716,19 @@
         <v>84</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3546,19 +3766,19 @@
         <v>84</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>82</v>
@@ -3570,7 +3790,7 @@
         <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>84</v>
@@ -3579,16 +3799,16 @@
         <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3599,10 +3819,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3610,13 +3830,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>95</v>
@@ -3628,16 +3848,16 @@
         <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>84</v>
@@ -3662,11 +3882,13 @@
         <v>84</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>84</v>
@@ -3684,10 +3906,10 @@
         <v>84</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>94</v>
@@ -3699,25 +3921,25 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -3725,10 +3947,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3736,34 +3958,34 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G15" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G15" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="H15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>84</v>
@@ -3788,35 +4010,37 @@
         <v>84</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>84</v>
@@ -3837,13 +4061,13 @@
         <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="AQ15" t="s" s="2">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="AR15" t="s" s="2">
         <v>84</v>
@@ -3851,35 +4075,33 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>194</v>
@@ -3901,10 +4123,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -3916,37 +4138,37 @@
         <v>84</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="Z16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>192</v>
-      </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>84</v>
@@ -3967,13 +4189,13 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3981,18 +4203,18 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>94</v>
@@ -4007,20 +4229,18 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>84</v>
       </c>
@@ -4032,7 +4252,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4044,13 +4264,13 @@
         <v>84</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>84</v>
@@ -4071,7 +4291,7 @@
         <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -4083,36 +4303,36 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>222</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4120,13 +4340,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>84</v>
@@ -4135,20 +4355,16 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>84</v>
       </c>
@@ -4196,7 +4412,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4217,19 +4433,19 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="AR18" t="s" s="2">
         <v>84</v>
@@ -4237,10 +4453,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4251,7 +4467,7 @@
         <v>82</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>84</v>
@@ -4263,16 +4479,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4322,13 +4538,13 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>84</v>
@@ -4349,13 +4565,13 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4363,21 +4579,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>84</v>
@@ -4389,19 +4605,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4450,13 +4664,13 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>84</v>
@@ -4471,19 +4685,19 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>249</v>
+        <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4491,24 +4705,24 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>84</v>
@@ -4517,20 +4731,18 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>84</v>
       </c>
@@ -4578,19 +4790,19 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>257</v>
+        <v>84</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>84</v>
@@ -4599,19 +4811,19 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4619,10 +4831,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4630,33 +4842,35 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>264</v>
+        <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
       </c>
@@ -4680,13 +4894,11 @@
         <v>84</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4704,10 +4916,10 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>94</v>
@@ -4719,25 +4931,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>84</v>
+        <v>250</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>84</v>
+        <v>251</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>84</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4745,10 +4957,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4756,32 +4968,34 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -4791,7 +5005,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -4806,31 +5020,29 @@
         <v>84</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -4845,25 +5057,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>276</v>
+        <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>277</v>
+        <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4871,18 +5083,20 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4894,22 +5108,22 @@
         <v>84</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>281</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -4919,7 +5133,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -4934,41 +5148,43 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -4980,37 +5196,35 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>290</v>
+        <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>94</v>
@@ -5025,19 +5239,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5062,13 +5276,13 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>84</v>
+        <v>277</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5086,51 +5300,51 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5153,13 +5367,13 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>297</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>299</v>
+        <v>163</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5210,7 +5424,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5240,7 +5454,7 @@
         <v>84</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5251,10 +5465,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5283,7 +5497,7 @@
         <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>304</v>
+        <v>167</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>143</v>
@@ -5324,19 +5538,19 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>305</v>
+        <v>168</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>306</v>
+        <v>169</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>307</v>
+        <v>171</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5366,7 +5580,7 @@
         <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5377,10 +5591,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5403,19 +5617,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5464,7 +5678,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5479,10 +5693,10 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>84</v>
@@ -5491,10 +5705,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5505,10 +5719,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5531,19 +5745,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>297</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5592,7 +5806,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5619,10 +5833,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5633,20 +5847,18 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
@@ -5661,19 +5873,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5722,7 +5934,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5731,42 +5943,42 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>287</v>
+        <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5777,32 +5989,30 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K31" t="s" s="2">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -5826,11 +6036,13 @@
         <v>84</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -5848,16 +6060,16 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>106</v>
@@ -5875,13 +6087,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>137</v>
+        <v>282</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -5889,21 +6101,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>84</v>
@@ -5912,22 +6124,22 @@
         <v>84</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>326</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5952,13 +6164,13 @@
         <v>84</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>213</v>
+        <v>84</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>347</v>
+        <v>84</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>84</v>
@@ -5976,13 +6188,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -5997,65 +6209,65 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>349</v>
+        <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>334</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>352</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6092,31 +6304,29 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>344</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
@@ -6125,19 +6335,19 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6145,14 +6355,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6162,27 +6374,29 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>193</v>
+        <v>351</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6206,13 +6420,13 @@
         <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>367</v>
+        <v>84</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -6230,7 +6444,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6239,42 +6453,42 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>344</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6288,29 +6502,27 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>193</v>
+        <v>355</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6334,13 +6546,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>377</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6358,7 +6570,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6373,10 +6585,10 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6385,13 +6597,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>363</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6399,10 +6611,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6413,30 +6625,30 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6484,13 +6696,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -6499,36 +6711,36 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>373</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6542,27 +6754,29 @@
         <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
       </c>
@@ -6598,19 +6812,17 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6619,10 +6831,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>106</v>
+        <v>381</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6634,29 +6846,31 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>398</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6665,31 +6879,31 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>400</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6738,19 +6952,19 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -6762,27 +6976,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6805,13 +7019,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>161</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
+        <v>163</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6862,7 +7076,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>300</v>
+        <v>164</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -6892,7 +7106,7 @@
         <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6903,10 +7117,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6935,7 +7149,7 @@
         <v>141</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>167</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>143</v>
@@ -6976,19 +7190,19 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>171</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7018,7 +7232,7 @@
         <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7029,14 +7243,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>411</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7046,28 +7260,28 @@
         <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>412</v>
+        <v>290</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>413</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>143</v>
+        <v>292</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>149</v>
+        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7116,7 +7330,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>414</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7128,13 +7342,13 @@
         <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>395</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>84</v>
@@ -7143,10 +7357,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>137</v>
+        <v>297</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7157,10 +7371,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7180,19 +7394,23 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>416</v>
+        <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>299</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7240,7 +7458,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7249,7 +7467,7 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
@@ -7267,10 +7485,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>420</v>
+        <v>304</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>421</v>
+        <v>305</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7281,12 +7499,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7298,25 +7518,29 @@
         <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>416</v>
+        <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>423</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7364,7 +7588,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>422</v>
+        <v>374</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7373,42 +7597,42 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>419</v>
+        <v>380</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>381</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>84</v>
+        <v>382</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>420</v>
+        <v>383</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7422,7 +7646,7 @@
         <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
@@ -7431,19 +7655,19 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7468,13 +7692,11 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7492,7 +7714,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7501,7 +7723,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7516,13 +7738,13 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>434</v>
+        <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7533,14 +7755,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7559,19 +7781,19 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7596,13 +7818,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>365</v>
+        <v>188</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7620,7 +7842,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7644,27 +7866,27 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7675,10 +7897,10 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -7687,17 +7909,19 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7746,13 +7970,13 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
@@ -7761,10 +7985,10 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>429</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -7773,10 +7997,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7787,10 +8011,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7813,15 +8037,17 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>297</v>
+        <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -7846,13 +8072,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>84</v>
+        <v>437</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -7870,7 +8096,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7894,27 +8120,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>439</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>442</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7925,7 +8151,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -7934,21 +8160,23 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>453</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -7972,13 +8200,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -7996,13 +8224,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8023,10 +8251,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8037,10 +8265,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8051,28 +8279,28 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8122,13 +8350,13 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
@@ -8137,36 +8365,36 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>458</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>84</v>
+        <v>459</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8177,7 +8405,7 @@
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8186,23 +8414,21 @@
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>400</v>
+        <v>464</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="N50" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>469</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8250,13 +8476,13 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
@@ -8274,19 +8500,19 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8305,7 +8531,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8317,16 +8543,20 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>297</v>
+        <v>473</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>298</v>
+        <v>474</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8374,19 +8604,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>300</v>
+        <v>472</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>84</v>
+        <v>478</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8401,10 +8631,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>301</v>
+        <v>480</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8415,21 +8645,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -8441,17 +8671,15 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8500,19 +8728,19 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>307</v>
+        <v>164</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8530,7 +8758,7 @@
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8541,14 +8769,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>411</v>
+        <v>139</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8561,26 +8789,24 @@
         <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>412</v>
+        <v>141</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>413</v>
+        <v>167</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8628,7 +8854,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>171</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8658,7 +8884,7 @@
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8669,45 +8895,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I54" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>478</v>
+        <v>143</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>212</v>
+        <v>149</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -8732,13 +8958,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>365</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -8756,22 +8982,22 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>480</v>
+        <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>84</v>
@@ -8780,16 +9006,16 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>481</v>
+        <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>219</v>
+        <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -8797,10 +9023,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8820,23 +9046,19 @@
         <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>281</v>
+        <v>489</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -8872,17 +9094,19 @@
         <v>84</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8891,7 +9115,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>84</v>
+        <v>492</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -8906,31 +9130,29 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>290</v>
+        <v>493</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>291</v>
+        <v>494</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>84</v>
       </c>
@@ -8942,29 +9164,25 @@
         <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>297</v>
+        <v>489</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9012,7 +9230,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9021,13 +9239,13 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>492</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
@@ -9036,27 +9254,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>290</v>
+        <v>493</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>291</v>
+        <v>498</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9079,19 +9297,19 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>337</v>
+        <v>503</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9116,13 +9334,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>213</v>
+        <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>338</v>
+        <v>505</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9140,7 +9358,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9149,7 +9367,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9164,13 +9382,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>84</v>
+        <v>506</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>137</v>
+        <v>507</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9181,14 +9399,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9198,7 +9416,7 @@
         <v>83</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>84</v>
@@ -9207,19 +9425,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>343</v>
+        <v>509</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>344</v>
+        <v>510</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>345</v>
+        <v>511</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>346</v>
+        <v>512</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9244,13 +9462,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>213</v>
+        <v>436</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>347</v>
+        <v>513</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>348</v>
+        <v>514</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9268,7 +9486,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9283,7 +9501,7 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>84</v>
@@ -9292,27 +9510,27 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>349</v>
+        <v>506</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>350</v>
+        <v>507</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>352</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9323,7 +9541,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -9335,19 +9553,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>85</v>
+        <v>516</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>404</v>
+        <v>519</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9396,13 +9612,13 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
@@ -9423,20 +9639,1670 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR59" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR60" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR61" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR62" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR63" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR64" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR65" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR66" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AC68" s="2"/>
+      <c r="AD68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O70" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AP59" t="s" s="2">
+      <c r="P70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AQ59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR59" t="s" s="2">
+      <c r="AA70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR72" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR59">
+  <autoFilter ref="A1:AR72">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9446,7 +11312,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (#63.05-.001)</t>
+    <t>1476: source value from MICROBIOLOGY - IEN (63.05-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -794,7 +794,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
   </si>
   <si>
-    <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
+    <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (63.05-11.5)</t>
   </si>
   <si>
     <t>Micro.Microbiology.BacteriologyReportStatus</t>
@@ -888,7 +888,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t>1525: fixed value = http://loinc.org#42803-7 Bacteria identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
+    <t>1525: fixed value = http://loinc.org#42803-7 Bacteria identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -937,7 +937,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case Not NULL</t>
+    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case Not NULL</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -989,7 +989,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1118,7 +1118,7 @@
 </t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
+    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
@@ -1140,7 +1140,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1171,7 +1171,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (#63.05-.04)</t>
+    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1249,7 +1249,7 @@
     <t>Observation.value[x].coding</t>
   </si>
   <si>
-    <t>1516: terminologyMaps using null on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
+    <t>1516: terminologyMaps using null on MICROBIOLOGY - URINE SCREEN (63.05-11.57)</t>
   </si>
   <si>
     <t>Micro.Microbiology.UrineScreen</t>
@@ -1267,7 +1267,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>1518: source value from MICROBIOLOGY - GRAM STAIN &gt; GRAM STAIN - GRAM STAIN (#63.05-11.6 &gt; 63.29-.01)</t>
+    <t>1518: source value from MICROBIOLOGY - GRAM STAIN &gt; GRAM STAIN - GRAM STAIN (63.05-11.6 &gt; 63.29-.01)</t>
   </si>
   <si>
     <t>Micro.BacteriologyReports.GramStain</t>
@@ -1355,7 +1355,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (#63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
+    <t>1455: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - COMMENT &gt; COMMENT - COMMENT (63.05-12 &gt; 63.3-2 &gt; 63.31-.01)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SpecimenComment</t>
@@ -1444,7 +1444,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (#63.05-.06)</t>
+    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
@@ -1748,7 +1748,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5+to+160)</t>
+    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1773,7 +1773,7 @@
     <t>Observation.component.value[x]:valueString</t>
   </si>
   <si>
-    <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5+to+160)</t>
+    <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -1799,7 +1799,7 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
-    <t>1524: terminologyMaps using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5.1+to+160.1)</t>
+    <t>1524: terminologyMaps using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5.1+to+160.1)</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -992,7 +992,7 @@
     <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1121,7 +1121,7 @@
     <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1172,6 +1172,9 @@
   </si>
   <si>
     <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -6714,22 +6717,22 @@
         <v>369</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6737,10 +6740,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6763,19 +6766,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6822,7 +6825,7 @@
         <v>170</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6831,10 +6834,10 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
@@ -6846,30 +6849,30 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
@@ -6894,16 +6897,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6952,7 +6955,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6961,10 +6964,10 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -6976,27 +6979,27 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7117,10 +7120,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7243,10 +7246,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7345,10 +7348,10 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>84</v>
@@ -7371,10 +7374,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7499,13 +7502,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>84</v>
@@ -7530,16 +7533,16 @@
         <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7588,7 +7591,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7597,42 +7600,42 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7658,16 +7661,16 @@
         <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7696,7 +7699,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7714,7 +7717,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7723,7 +7726,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7744,7 +7747,7 @@
         <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7755,14 +7758,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7784,16 +7787,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7821,10 +7824,10 @@
         <v>188</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7842,7 +7845,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7866,27 +7869,27 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7909,19 +7912,19 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7970,7 +7973,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7985,10 +7988,10 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -7997,10 +8000,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8011,10 +8014,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8040,13 +8043,13 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8072,13 +8075,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8096,7 +8099,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8120,27 +8123,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8166,16 +8169,16 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8200,13 +8203,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8224,7 +8227,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8251,10 +8254,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8265,10 +8268,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8291,16 +8294,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8350,7 +8353,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8365,36 +8368,36 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8417,16 +8420,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8476,7 +8479,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8500,27 +8503,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8543,19 +8546,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8604,7 +8607,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8616,7 +8619,7 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8631,10 +8634,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8645,10 +8648,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8769,10 +8772,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8895,14 +8898,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8924,10 +8927,10 @@
         <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8982,7 +8985,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9023,10 +9026,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9049,13 +9052,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9106,7 +9109,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9115,7 +9118,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9133,10 +9136,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9147,10 +9150,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9173,13 +9176,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9230,7 +9233,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9239,7 +9242,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9257,10 +9260,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9271,10 +9274,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9300,16 +9303,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9337,10 +9340,10 @@
         <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9358,7 +9361,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9382,13 +9385,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9399,10 +9402,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9428,16 +9431,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9462,13 +9465,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9486,7 +9489,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9510,13 +9513,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9527,10 +9530,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9553,17 +9556,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9612,7 +9615,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9642,7 +9645,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9653,10 +9656,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9682,10 +9685,10 @@
         <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9736,7 +9739,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9763,10 +9766,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9777,10 +9780,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9803,16 +9806,16 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9862,7 +9865,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9889,10 +9892,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9903,10 +9906,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9929,16 +9932,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9988,7 +9991,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10015,10 +10018,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10029,10 +10032,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10055,19 +10058,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10116,7 +10119,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10143,10 +10146,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10157,10 +10160,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10281,10 +10284,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10407,14 +10410,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10436,10 +10439,10 @@
         <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10494,7 +10497,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10535,10 +10538,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10564,13 +10567,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>276</v>
@@ -10598,10 +10601,10 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>278</v>
@@ -10622,7 +10625,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -10637,7 +10640,7 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>84</v>
@@ -10646,7 +10649,7 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>282</v>
@@ -10663,10 +10666,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10689,19 +10692,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10748,7 +10751,7 @@
         <v>170</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10772,30 +10775,30 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>84</v>
@@ -10820,16 +10823,16 @@
         <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10878,7 +10881,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10893,7 +10896,7 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>84</v>
@@ -10902,27 +10905,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10948,16 +10951,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10985,10 +10988,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11006,7 +11009,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11015,7 +11018,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11036,7 +11039,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11047,14 +11050,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11076,16 +11079,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11113,10 +11116,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11134,7 +11137,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11149,7 +11152,7 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>84</v>
@@ -11158,27 +11161,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11204,16 +11207,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11262,7 +11265,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11289,10 +11292,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3311" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1721,6 +1721,10 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:code}
+</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1749,9 +1753,6 @@
   </si>
   <si>
     <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1773,12 +1774,6 @@
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>Observation.component.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
-  </si>
-  <si>
     <t>Observation.component.dataAbsentReason</t>
   </si>
   <si>
@@ -1802,16 +1797,55 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
+    <t>Observation.component.referenceRange</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation of component result</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component</t>
+  </si>
+  <si>
+    <t>va-component</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code</t>
+  </si>
+  <si>
+    <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.interpretation</t>
+  </si>
+  <si>
     <t>1524: terminologyMaps using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5.1+to+160.1)</t>
   </si>
   <si>
-    <t>Observation.component.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+    <t>Observation.component:va-component.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2128,10 +2162,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR72"/>
+  <dimension ref="A1:AR81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -10107,16 +10141,14 @@
         <v>84</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>539</v>
@@ -10146,10 +10178,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10160,10 +10192,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10284,10 +10316,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10410,10 +10442,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10538,10 +10570,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10555,7 +10587,7 @@
         <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>84</v>
@@ -10567,13 +10599,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>276</v>
@@ -10604,7 +10636,7 @@
         <v>437</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Z67" t="s" s="2">
         <v>278</v>
@@ -10625,7 +10657,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -10640,7 +10672,7 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>84</v>
@@ -10741,14 +10773,16 @@
         <v>84</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC68" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
         <v>556</v>
@@ -10795,11 +10829,9 @@
         <v>561</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10811,28 +10843,28 @@
         <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10857,13 +10889,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10881,7 +10913,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10890,13 +10922,13 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>562</v>
+        <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>84</v>
@@ -10905,38 +10937,38 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>384</v>
+        <v>137</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>84</v>
@@ -10951,16 +10983,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>564</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>565</v>
+        <v>414</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>566</v>
+        <v>415</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10988,37 +11020,37 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>563</v>
-      </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>568</v>
+        <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11033,31 +11065,31 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>84</v>
+        <v>419</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>137</v>
+        <v>420</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>84</v>
+        <v>422</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>412</v>
+        <v>84</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11067,7 +11099,7 @@
         <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>84</v>
@@ -11076,19 +11108,19 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>413</v>
+        <v>569</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>414</v>
+        <v>570</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>415</v>
+        <v>477</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>416</v>
+        <v>478</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11113,13 +11145,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11137,7 +11169,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11152,7 +11184,7 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>84</v>
@@ -11161,19 +11193,19 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>422</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" hidden="true">
@@ -11181,9 +11213,11 @@
         <v>571</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11192,7 +11226,7 @@
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>84</v>
@@ -11201,22 +11235,22 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>572</v>
+        <v>540</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>573</v>
+        <v>541</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>477</v>
+        <v>542</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>478</v>
+        <v>543</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11265,7 +11299,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>571</v>
+        <v>539</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11292,20 +11326,1166 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AC77" s="2"/>
+      <c r="AD77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AQ80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR80" t="s" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AP72" t="s" s="2">
+      <c r="AP81" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AQ72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR72" t="s" s="2">
+      <c r="AQ81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR81" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR72">
+  <autoFilter ref="A1:AR81">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11315,7 +12495,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$99</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3311" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="655">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,10 +632,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -944,6 +950,136 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1480-2: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1480-3: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) case Not NULL</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1825,6 +1961,81 @@
   </si>
   <si>
     <t>1522: transform using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>1522-2: fixed value = http://loinc.org</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.code</t>
+  </si>
+  <si>
+    <t>1522-1: fixed value without value?</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.component:va-component.code.text</t>
+  </si>
+  <si>
+    <t>Observation.component.code.text</t>
   </si>
   <si>
     <t>Observation.component:va-component.value[x]</t>
@@ -2162,11 +2373,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR81"/>
+  <dimension ref="A1:AR99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="61.265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -4129,7 +4340,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -4160,10 +4371,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -4199,7 +4410,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4214,7 +4425,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4226,10 +4437,10 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4240,10 +4451,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4269,13 +4480,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4289,7 +4500,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4325,7 +4536,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4340,7 +4551,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -4352,10 +4563,10 @@
         <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4366,10 +4577,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4392,13 +4603,13 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4449,7 +4660,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4476,10 +4687,10 @@
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4490,10 +4701,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4516,16 +4727,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4575,7 +4786,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4602,10 +4813,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4616,14 +4827,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4642,17 +4853,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4701,7 +4912,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4722,16 +4933,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4742,14 +4953,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4768,16 +4979,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4827,7 +5038,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4848,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4868,10 +5079,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4897,16 +5108,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4935,7 +5146,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4953,7 +5164,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>94</v>
@@ -4968,25 +5179,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4994,10 +5205,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5023,16 +5234,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5042,7 +5253,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5060,16 +5271,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5079,7 +5290,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5094,7 +5305,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5109,10 +5320,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5120,13 +5331,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5151,16 +5362,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5170,7 +5381,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5188,10 +5399,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5209,7 +5420,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5239,10 +5450,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5250,14 +5461,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5279,16 +5490,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5316,10 +5527,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5337,7 +5548,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5352,36 +5563,36 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5502,10 +5713,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5628,10 +5839,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5654,19 +5865,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5715,7 +5926,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5730,7 +5941,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5742,10 +5953,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5756,10 +5967,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5779,23 +5990,19 @@
         <v>84</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>162</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>84</v>
       </c>
@@ -5843,7 +6050,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>303</v>
+        <v>164</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5855,7 +6062,7 @@
         <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>84</v>
@@ -5870,10 +6077,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>165</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5884,46 +6091,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>307</v>
+        <v>140</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>308</v>
+        <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
+        <v>167</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -5959,52 +6164,52 @@
         <v>84</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>313</v>
+        <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>315</v>
+        <v>84</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>316</v>
+        <v>165</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6012,10 +6217,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6026,10 +6231,10 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6038,18 +6243,20 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6097,13 +6304,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6112,7 +6319,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6124,13 +6331,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6138,14 +6345,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6164,20 +6371,18 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>84</v>
       </c>
@@ -6225,7 +6430,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6246,19 +6451,19 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>84</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6266,14 +6471,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6292,19 +6497,17 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6341,17 +6544,19 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6360,31 +6565,31 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6392,16 +6597,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6420,19 +6623,17 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>351</v>
+        <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6481,7 +6682,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6490,31 +6691,31 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6522,10 +6723,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6539,7 +6740,7 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
@@ -6548,18 +6749,20 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6607,7 +6810,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6622,10 +6825,10 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>84</v>
@@ -6634,13 +6837,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>363</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6648,10 +6851,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6662,10 +6865,10 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -6674,17 +6877,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>365</v>
+        <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6733,13 +6938,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -6748,25 +6953,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6774,10 +6979,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6785,7 +6990,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6800,19 +7005,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6849,17 +7054,19 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6868,46 +7075,44 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6916,10 +7121,10 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
@@ -6928,20 +7133,18 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>364</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6989,19 +7192,19 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
@@ -7013,31 +7216,31 @@
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>384</v>
+        <v>284</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>84</v>
+        <v>370</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7053,19 +7256,23 @@
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>161</v>
+        <v>371</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>162</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7113,7 +7320,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7125,7 +7332,7 @@
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7134,19 +7341,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>165</v>
+        <v>378</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7154,44 +7361,46 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>139</v>
+        <v>381</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>140</v>
+        <v>382</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>141</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>167</v>
+        <v>384</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7227,11 +7436,9 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7239,19 +7446,19 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>389</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7260,19 +7467,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>165</v>
+        <v>392</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7280,21 +7487,23 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="D41" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>95</v>
@@ -7306,19 +7515,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>289</v>
+        <v>396</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>290</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>291</v>
+        <v>384</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>292</v>
+        <v>385</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>293</v>
+        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7367,40 +7576,40 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>294</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>84</v>
+        <v>388</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>296</v>
+        <v>391</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>297</v>
+        <v>392</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7408,10 +7617,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7425,7 +7634,7 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
@@ -7434,20 +7643,18 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>161</v>
+        <v>400</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>299</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>300</v>
+        <v>402</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7495,7 +7702,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7510,10 +7717,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7522,13 +7729,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>304</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>305</v>
+        <v>407</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7536,14 +7743,12 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7552,7 +7757,7 @@
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>95</v>
@@ -7564,19 +7769,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>161</v>
+        <v>410</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>380</v>
+        <v>413</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7625,51 +7828,51 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>409</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>382</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>384</v>
+        <v>417</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>385</v>
+        <v>418</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7689,22 +7892,22 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>183</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7729,29 +7932,29 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7760,10 +7963,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7775,62 +7978,64 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>137</v>
+        <v>429</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="D45" t="s" s="2">
-        <v>412</v>
+        <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7855,13 +8060,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7879,19 +8084,19 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -7903,27 +8108,27 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7934,10 +8139,10 @@
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -7946,20 +8151,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>424</v>
+        <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>162</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8007,25 +8208,25 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>423</v>
+        <v>164</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -8034,10 +8235,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>432</v>
+        <v>165</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8048,21 +8249,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -8074,16 +8275,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>434</v>
+        <v>141</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>435</v>
+        <v>167</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>436</v>
+        <v>143</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8109,43 +8310,43 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>438</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>439</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>433</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -8157,27 +8358,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>441</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>442</v>
+        <v>165</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8188,31 +8389,31 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>291</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>445</v>
+        <v>292</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>446</v>
+        <v>293</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>447</v>
+        <v>294</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>448</v>
+        <v>295</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8237,13 +8438,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8261,13 +8462,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>444</v>
+        <v>296</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8276,10 +8477,10 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
@@ -8288,10 +8489,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>451</v>
+        <v>298</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>452</v>
+        <v>299</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8302,10 +8503,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8319,27 +8520,29 @@
         <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>454</v>
+        <v>161</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>455</v>
+        <v>344</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>456</v>
+        <v>345</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8387,7 +8590,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>453</v>
+        <v>348</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8402,38 +8605,40 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>461</v>
+        <v>349</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>462</v>
+        <v>350</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8445,27 +8650,29 @@
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>465</v>
+        <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>467</v>
+        <v>423</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8513,7 +8720,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>464</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8522,42 +8729,42 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>84</v>
+        <v>426</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>447</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>469</v>
+        <v>428</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>470</v>
+        <v>429</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>471</v>
+        <v>430</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>472</v>
+        <v>431</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8568,10 +8775,10 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>84</v>
@@ -8580,19 +8787,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>474</v>
+        <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8617,13 +8824,11 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8641,19 +8846,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>473</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>84</v>
+        <v>454</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>479</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8668,10 +8873,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>480</v>
+        <v>137</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8682,21 +8887,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -8708,16 +8913,20 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>162</v>
+        <v>458</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8741,13 +8950,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8765,19 +8974,19 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>164</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8789,31 +8998,31 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>84</v>
+        <v>465</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>165</v>
+        <v>466</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
+        <v>467</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8823,7 +9032,7 @@
         <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
@@ -8832,18 +9041,20 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>140</v>
+        <v>469</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>141</v>
+        <v>470</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>167</v>
+        <v>471</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8891,7 +9102,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>171</v>
+        <v>468</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8903,13 +9114,13 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>84</v>
+        <v>474</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>84</v>
+        <v>475</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>84</v>
@@ -8918,10 +9129,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>165</v>
+        <v>477</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8932,46 +9143,44 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -8995,13 +9204,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9019,43 +9228,43 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR54" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR54" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -9086,16 +9295,20 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9119,13 +9332,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>84</v>
+        <v>494</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9152,7 +9365,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>493</v>
+        <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9170,10 +9383,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9184,10 +9397,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9201,7 +9414,7 @@
         <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>84</v>
@@ -9210,15 +9423,17 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9267,7 +9482,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9276,42 +9491,42 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>493</v>
+        <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>84</v>
+        <v>503</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>84</v>
+        <v>504</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>84</v>
+        <v>505</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9334,20 +9549,18 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>183</v>
+        <v>510</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9371,13 +9584,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>505</v>
+        <v>84</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>506</v>
+        <v>84</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9395,7 +9608,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9419,27 +9632,27 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>421</v>
+        <v>516</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>84</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9462,19 +9675,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>183</v>
+        <v>519</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9499,13 +9712,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>514</v>
+        <v>84</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>515</v>
+        <v>84</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9523,7 +9736,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9535,7 +9748,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>524</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9547,13 +9760,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>507</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>421</v>
+        <v>526</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9564,10 +9777,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9590,18 +9803,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>517</v>
+        <v>161</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>518</v>
+        <v>162</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>519</v>
+        <v>163</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>520</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9649,7 +9860,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>516</v>
+        <v>164</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9661,7 +9872,7 @@
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9679,7 +9890,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>521</v>
+        <v>165</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9690,21 +9901,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
@@ -9716,15 +9927,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>523</v>
+        <v>141</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9773,19 +9986,19 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>522</v>
+        <v>171</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -9800,10 +10013,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>525</v>
+        <v>165</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9814,14 +10027,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>84</v>
+        <v>530</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9834,24 +10047,26 @@
         <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>527</v>
+        <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9899,7 +10114,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9911,7 +10126,7 @@
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -9926,10 +10141,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>531</v>
+        <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>532</v>
+        <v>137</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9940,10 +10155,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9954,7 +10169,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -9963,20 +10178,18 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N62" t="s" s="2">
         <v>537</v>
       </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10025,16 +10238,16 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>84</v>
+        <v>538</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10052,10 +10265,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10066,10 +10279,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10080,7 +10293,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -10089,23 +10302,19 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>474</v>
+        <v>535</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O63" t="s" s="2">
         <v>543</v>
       </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10141,26 +10350,28 @@
         <v>84</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>84</v>
+        <v>538</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10178,10 +10389,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10192,10 +10403,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10218,16 +10429,20 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>162</v>
+        <v>546</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10251,13 +10466,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>84</v>
+        <v>550</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>84</v>
+        <v>551</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10275,7 +10490,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>164</v>
+        <v>545</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10287,7 +10502,7 @@
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10299,13 +10514,13 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>84</v>
+        <v>552</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>84</v>
+        <v>553</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>165</v>
+        <v>466</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10316,14 +10531,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10342,18 +10557,20 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>141</v>
+        <v>555</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>167</v>
+        <v>556</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10377,13 +10594,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>84</v>
+        <v>559</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>84</v>
+        <v>560</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10401,7 +10618,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>171</v>
+        <v>554</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10413,7 +10630,7 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10425,13 +10642,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>84</v>
+        <v>552</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>84</v>
+        <v>553</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>165</v>
+        <v>466</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10442,45 +10659,43 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>140</v>
+        <v>562</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>486</v>
+        <v>563</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>149</v>
+        <v>565</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10529,19 +10744,19 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>488</v>
+        <v>561</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10559,7 +10774,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>137</v>
+        <v>566</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10570,10 +10785,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10581,7 +10796,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>94</v>
@@ -10593,23 +10808,19 @@
         <v>84</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10633,13 +10844,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10657,10 +10868,10 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>94</v>
@@ -10681,16 +10892,16 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>555</v>
+        <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>282</v>
+        <v>539</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>283</v>
+        <v>570</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -10698,10 +10909,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10712,7 +10923,7 @@
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
@@ -10724,20 +10935,18 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>376</v>
+        <v>572</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10785,13 +10994,13 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
@@ -10809,27 +11018,27 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>384</v>
+        <v>576</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>385</v>
+        <v>577</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10840,7 +11049,7 @@
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -10849,23 +11058,21 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>183</v>
+        <v>579</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10889,13 +11096,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10913,16 +11120,16 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>561</v>
+        <v>578</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10940,10 +11147,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>137</v>
+        <v>576</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>410</v>
+        <v>583</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10954,14 +11161,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>412</v>
+        <v>84</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10977,22 +11184,22 @@
         <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>183</v>
+        <v>519</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>585</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>586</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>415</v>
+        <v>587</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>416</v>
+        <v>588</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11017,31 +11224,29 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11065,27 +11270,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>420</v>
+        <v>590</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>421</v>
+        <v>591</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>422</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11096,7 +11301,7 @@
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11108,20 +11313,16 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>569</v>
+        <v>162</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11169,19 +11370,19 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>568</v>
+        <v>164</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11196,10 +11397,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>480</v>
+        <v>84</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>481</v>
+        <v>165</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11210,23 +11411,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>84</v>
@@ -11235,23 +11434,21 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>474</v>
+        <v>140</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>540</v>
+        <v>141</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>541</v>
+        <v>167</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11299,7 +11496,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>539</v>
+        <v>171</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11311,7 +11508,7 @@
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11326,10 +11523,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>545</v>
+        <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>546</v>
+        <v>165</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11340,42 +11537,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>84</v>
+        <v>530</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>162</v>
+        <v>531</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -11423,19 +11624,19 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>164</v>
+        <v>533</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
@@ -11453,7 +11654,7 @@
         <v>84</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11464,21 +11665,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>84</v>
@@ -11487,21 +11688,23 @@
         <v>84</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>141</v>
+        <v>596</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>167</v>
+        <v>597</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
@@ -11525,13 +11728,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11549,19 +11752,19 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>171</v>
+        <v>595</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -11573,16 +11776,16 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>84</v>
+        <v>600</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>84</v>
+        <v>286</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>84</v>
@@ -11590,45 +11793,45 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>549</v>
+        <v>601</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>140</v>
+        <v>421</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>486</v>
+        <v>602</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>487</v>
+        <v>603</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>143</v>
+        <v>604</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>149</v>
+        <v>425</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11677,19 +11880,19 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>488</v>
+        <v>601</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>84</v>
@@ -11701,27 +11904,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>84</v>
+        <v>605</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>84</v>
+        <v>429</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>137</v>
+        <v>430</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11729,34 +11932,34 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>551</v>
+        <v>607</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>552</v>
+        <v>608</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>553</v>
+        <v>609</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>276</v>
+        <v>452</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11781,13 +11984,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>437</v>
+        <v>188</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>554</v>
+        <v>610</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>278</v>
+        <v>453</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11805,22 +12008,22 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>84</v>
+        <v>611</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>577</v>
+        <v>84</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>84</v>
@@ -11829,16 +12032,16 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>555</v>
+        <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>282</v>
+        <v>137</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>84</v>
@@ -11846,21 +12049,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>578</v>
+        <v>612</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>556</v>
+        <v>612</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>84</v>
@@ -11869,22 +12072,22 @@
         <v>84</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>376</v>
+        <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>557</v>
+        <v>458</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>558</v>
+        <v>459</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>559</v>
+        <v>460</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>380</v>
+        <v>461</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -11909,35 +12112,37 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC77" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>556</v>
+        <v>612</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>84</v>
@@ -11955,31 +12160,29 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>560</v>
+        <v>464</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>384</v>
+        <v>465</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>385</v>
+        <v>466</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>386</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>579</v>
+        <v>613</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>84</v>
       </c>
@@ -11988,31 +12191,31 @@
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>557</v>
+        <v>614</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>558</v>
+        <v>615</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>559</v>
+        <v>522</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>380</v>
+        <v>523</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12061,13 +12264,13 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>556</v>
+        <v>613</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>84</v>
@@ -12076,7 +12279,7 @@
         <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>580</v>
+        <v>84</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>84</v>
@@ -12085,29 +12288,31 @@
         <v>84</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>384</v>
+        <v>525</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>385</v>
+        <v>526</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>581</v>
+        <v>616</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>84</v>
       </c>
@@ -12125,22 +12330,22 @@
         <v>84</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>183</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>563</v>
+        <v>586</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>564</v>
+        <v>587</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>407</v>
+        <v>588</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12165,13 +12370,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>565</v>
+        <v>84</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12189,16 +12394,16 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -12216,10 +12421,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>137</v>
+        <v>590</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>410</v>
+        <v>591</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12230,24 +12435,24 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>582</v>
+        <v>618</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>567</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>412</v>
+        <v>84</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>84</v>
@@ -12256,20 +12461,16 @@
         <v>84</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>413</v>
+        <v>162</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12293,13 +12494,13 @@
         <v>84</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12317,22 +12518,22 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>567</v>
+        <v>164</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>583</v>
+        <v>84</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>84</v>
@@ -12341,31 +12542,31 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>419</v>
+        <v>84</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>421</v>
+        <v>165</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>422</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>584</v>
+        <v>619</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12384,20 +12585,18 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>569</v>
+        <v>141</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>570</v>
+        <v>167</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>84</v>
       </c>
@@ -12445,7 +12644,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>568</v>
+        <v>171</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -12457,35 +12656,2321 @@
         <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR81" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR82" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AQ81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR81" t="s" s="2">
+      <c r="AK83" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AR83" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR84" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR85" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR86" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR87" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR88" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AP89" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AQ89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR89" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AQ90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR90" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AQ91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR91" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AQ92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR92" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AQ93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR93" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR94" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AC95" s="2"/>
+      <c r="AD95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR95" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR96" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR97" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR98" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR99" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR81">
+  <autoFilter ref="A1:AR99">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12495,7 +14980,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI80">
+  <conditionalFormatting sqref="A2:AI98">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>http://va.gov/identifiers/$Sta3n/63.05</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1476-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/$fileNr</t>
+    <t>1476-1: fixed value = http://va.gov/identifiers/$Sta3n/63.05</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4034" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,13 +797,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
-  </si>
-  <si>
-    <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (63.05-11.5)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.BacteriologyReportStatus</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -2401,7 +2395,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5179,25 +5173,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -5205,10 +5199,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5234,16 +5228,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5253,7 +5247,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5271,16 +5265,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5290,7 +5284,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5305,25 +5299,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5331,13 +5325,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5362,16 +5356,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5381,7 +5375,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5399,10 +5393,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5420,7 +5414,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5450,10 +5444,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5461,14 +5455,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5490,16 +5484,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5527,10 +5521,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5548,7 +5542,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5563,36 +5557,36 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5713,10 +5707,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5839,10 +5833,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5865,19 +5859,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5926,7 +5920,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5941,22 +5935,22 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5967,10 +5961,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6091,10 +6085,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6217,10 +6211,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6246,16 +6240,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6304,7 +6298,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6319,22 +6313,22 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6345,10 +6339,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6374,13 +6368,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6430,7 +6424,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6457,10 +6451,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6471,10 +6465,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6500,14 +6494,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6556,7 +6550,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6571,22 +6565,22 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6597,10 +6591,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6626,14 +6620,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6682,7 +6676,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6697,22 +6691,22 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6723,10 +6717,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6749,19 +6743,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6810,7 +6804,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6837,10 +6831,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6851,10 +6845,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6880,16 +6874,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6938,7 +6932,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6965,10 +6959,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6979,10 +6973,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7005,19 +6999,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7066,7 +7060,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7081,25 +7075,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -7107,10 +7101,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7133,16 +7127,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7192,7 +7186,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7219,13 +7213,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7233,14 +7227,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7259,19 +7253,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7320,7 +7314,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7341,19 +7335,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AN39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7361,14 +7355,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7387,19 +7381,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7436,7 +7430,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7446,7 +7440,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7455,31 +7449,31 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7487,16 +7481,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7515,19 +7509,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7576,7 +7570,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7585,31 +7579,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AJ41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AK41" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7617,10 +7611,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7643,16 +7637,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7702,7 +7696,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7717,25 +7711,25 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7743,10 +7737,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7769,17 +7763,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7828,7 +7822,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7843,25 +7837,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7869,10 +7863,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7895,19 +7889,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7944,7 +7938,7 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7954,7 +7948,7 @@
         <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7963,45 +7957,45 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AJ44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -8026,16 +8020,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8084,7 +8078,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8093,42 +8087,42 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AJ45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AK45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AO45" t="s" s="2">
+      <c r="AQ45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR45" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8249,10 +8243,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8375,10 +8369,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8401,19 +8395,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8462,7 +8456,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8477,10 +8471,10 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
@@ -8489,10 +8483,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8503,10 +8497,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8532,16 +8526,16 @@
         <v>161</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8590,7 +8584,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8617,10 +8611,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8631,13 +8625,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>84</v>
@@ -8662,16 +8656,16 @@
         <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8720,7 +8714,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8729,42 +8723,42 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AJ50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AK50" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8790,16 +8784,16 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8828,7 +8822,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8846,7 +8840,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8855,7 +8849,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8876,7 +8870,7 @@
         <v>137</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8887,14 +8881,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8916,16 +8910,16 @@
         <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8953,10 +8947,10 @@
         <v>188</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8974,7 +8968,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8998,27 +8992,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AQ52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR52" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9041,19 +9035,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9102,7 +9096,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9117,22 +9111,22 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AP53" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9143,10 +9137,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9172,13 +9166,13 @@
         <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9204,14 +9198,14 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="Y54" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9228,7 +9222,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9252,27 +9246,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AQ54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR54" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR54" t="s" s="2">
-        <v>488</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9298,16 +9292,16 @@
         <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9332,13 +9326,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9356,7 +9350,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9383,10 +9377,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9397,10 +9391,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9423,16 +9417,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9482,7 +9476,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9497,36 +9491,36 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AO56" t="s" s="2">
+      <c r="AQ56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9549,16 +9543,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9608,7 +9602,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9632,27 +9626,27 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AO57" t="s" s="2">
+      <c r="AQ57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR57" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR57" t="s" s="2">
-        <v>517</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9675,19 +9669,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9736,7 +9730,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9748,25 +9742,25 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9777,10 +9771,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9901,10 +9895,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10027,14 +10021,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10056,10 +10050,10 @@
         <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>143</v>
@@ -10114,7 +10108,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10155,10 +10149,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10181,13 +10175,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10238,7 +10232,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10247,7 +10241,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10265,10 +10259,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10279,10 +10273,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10305,13 +10299,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10362,7 +10356,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10371,7 +10365,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10389,10 +10383,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10403,10 +10397,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10432,16 +10426,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10469,10 +10463,10 @@
         <v>118</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10490,7 +10484,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10514,13 +10508,13 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10531,10 +10525,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10560,16 +10554,16 @@
         <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10594,13 +10588,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10618,7 +10612,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10642,13 +10636,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10659,10 +10653,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10685,17 +10679,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10744,7 +10738,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10774,7 +10768,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10785,10 +10779,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10814,10 +10808,10 @@
         <v>161</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10868,7 +10862,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10895,10 +10889,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10909,10 +10903,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10935,16 +10929,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10994,7 +10988,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11021,10 +11015,10 @@
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11035,10 +11029,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11061,16 +11055,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11120,7 +11114,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11147,10 +11141,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11161,10 +11155,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11187,19 +11181,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11236,7 +11230,7 @@
         <v>84</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
@@ -11246,7 +11240,7 @@
         <v>170</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11273,10 +11267,10 @@
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11287,10 +11281,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11411,10 +11405,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11537,14 +11531,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11566,10 +11560,10 @@
         <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>143</v>
@@ -11624,7 +11618,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11665,10 +11659,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11694,16 +11688,16 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M74" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="O74" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11728,13 +11722,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11752,7 +11746,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>94</v>
@@ -11776,16 +11770,16 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AO74" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>84</v>
@@ -11793,10 +11787,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11819,19 +11813,19 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11880,7 +11874,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11904,27 +11898,27 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AO75" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11950,16 +11944,16 @@
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M76" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="O76" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11987,10 +11981,10 @@
         <v>188</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12008,7 +12002,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12017,7 +12011,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -12038,7 +12032,7 @@
         <v>137</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12049,14 +12043,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12078,16 +12072,16 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12115,10 +12109,10 @@
         <v>188</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12136,7 +12130,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12160,27 +12154,27 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AQ77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR77" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12206,16 +12200,16 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12264,7 +12258,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12291,10 +12285,10 @@
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12305,13 +12299,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>84</v>
@@ -12333,19 +12327,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="O79" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12394,7 +12388,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12421,10 +12415,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12435,10 +12429,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12559,10 +12553,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12685,14 +12679,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12714,10 +12708,10 @@
         <v>140</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>143</v>
@@ -12772,7 +12766,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12813,10 +12807,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12842,16 +12836,16 @@
         <v>183</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="M83" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="O83" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -12876,13 +12870,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -12900,7 +12894,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>94</v>
@@ -12915,7 +12909,7 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>84</v>
@@ -12924,16 +12918,16 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AO83" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>84</v>
@@ -12941,10 +12935,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13065,10 +13059,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13191,10 +13185,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13217,19 +13211,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13278,7 +13272,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13305,10 +13299,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13319,10 +13313,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13443,10 +13437,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13569,10 +13563,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13598,16 +13592,16 @@
         <v>108</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13617,7 +13611,7 @@
         <v>84</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>84</v>
@@ -13656,7 +13650,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13671,7 +13665,7 @@
         <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>84</v>
@@ -13683,10 +13677,10 @@
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
@@ -13697,10 +13691,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13726,13 +13720,13 @@
         <v>161</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13782,7 +13776,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13809,10 +13803,10 @@
         <v>84</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
@@ -13823,10 +13817,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13852,14 +13846,14 @@
         <v>114</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13908,7 +13902,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13923,7 +13917,7 @@
         <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>84</v>
@@ -13935,10 +13929,10 @@
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -13949,10 +13943,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13978,14 +13972,14 @@
         <v>161</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14034,7 +14028,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14061,10 +14055,10 @@
         <v>84</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14075,10 +14069,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14101,19 +14095,19 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14162,7 +14156,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14189,10 +14183,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14203,10 +14197,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14232,16 +14226,16 @@
         <v>161</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="O94" t="s" s="2">
         <v>345</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14290,7 +14284,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14317,10 +14311,10 @@
         <v>84</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14331,10 +14325,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14357,19 +14351,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14406,7 +14400,7 @@
         <v>84</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
@@ -14416,7 +14410,7 @@
         <v>170</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14440,30 +14434,30 @@
         <v>84</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>84</v>
@@ -14488,16 +14482,16 @@
         <v>161</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="O96" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14546,7 +14540,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14561,7 +14555,7 @@
         <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>84</v>
@@ -14570,27 +14564,27 @@
         <v>84</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AO96" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR96" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14616,16 +14610,16 @@
         <v>183</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>609</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -14653,10 +14647,10 @@
         <v>188</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>84</v>
@@ -14674,7 +14668,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -14683,7 +14677,7 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>106</v>
@@ -14704,7 +14698,7 @@
         <v>137</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -14715,14 +14709,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -14744,16 +14738,16 @@
         <v>183</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="O98" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -14781,10 +14775,10 @@
         <v>188</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -14802,7 +14796,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -14817,7 +14811,7 @@
         <v>106</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>84</v>
@@ -14826,27 +14820,27 @@
         <v>84</v>
       </c>
       <c r="AN98" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AO98" t="s" s="2">
+      <c r="AQ98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR98" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14872,16 +14866,16 @@
         <v>85</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -14930,7 +14924,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -14957,10 +14951,10 @@
         <v>84</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
